--- a/docs/StructureDefinition-LTCPractitioner.xlsx
+++ b/docs/StructureDefinition-LTCPractitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T05:34:23+08:00</t>
+    <t>2026-02-28T07:16:04+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LTCPractitioner.xlsx
+++ b/docs/StructureDefinition-LTCPractitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T07:16:04+08:00</t>
+    <t>2026-02-28T23:13:53+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LTCPractitioner.xlsx
+++ b/docs/StructureDefinition-LTCPractitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.1</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T23:13:53+08:00</t>
+    <t>2026-03-01T19:25:35+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LTCPractitioner.xlsx
+++ b/docs/StructureDefinition-LTCPractitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T19:25:35+08:00</t>
+    <t>2026-03-02T02:26:08+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LTCPractitioner.xlsx
+++ b/docs/StructureDefinition-LTCPractitioner.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4621" uniqueCount="610">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4620" uniqueCount="612">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T02:26:08+08:00</t>
+    <t>2026-04-02T13:32:15+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -633,14 +633,7 @@
     <t>Identifier.type</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>CE/CNE/CWE</t>
-  </si>
-  <si>
-    <t>CD</t>
+    <t>CX.5</t>
   </si>
   <si>
     <t>Practitioner.identifier:idCardNumber.type.id</t>
@@ -689,10 +682,10 @@
     <t>CodeableConcept.coding</t>
   </si>
   <si>
-    <t>CE/CNE/CWE subset one of the sets of component 1-3 or 4-6</t>
-  </si>
-  <si>
-    <t>CV</t>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
   </si>
   <si>
     <t>Practitioner.identifier:idCardNumber.type.coding.id</t>
@@ -837,6 +830,10 @@
     <t xml:space="preserve">
 - 增加Practitioner.identifier.type.coding.code欄位也可使用此Extension，以利實務專案使用  
 識別碼後綴詞</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
   </si>
   <si>
     <t>Practitioner.identifier:idCardNumber.type.coding.code.value</t>
@@ -1715,13 +1712,13 @@
     <t>Administrative Gender為行政管理的及保存紀錄目的之健康照護服務提供者性別</t>
   </si>
   <si>
-    <t>XAD</t>
-  </si>
-  <si>
-    <t>AD</t>
-  </si>
-  <si>
-    <t>Address</t>
+    <t>ORC-24, STF-11, ROL-11, PRT-14</t>
+  </si>
+  <si>
+    <t>./addr</t>
+  </si>
+  <si>
+    <t>./Addresses</t>
   </si>
   <si>
     <t>Practitioner.gender</t>
@@ -1855,15 +1852,15 @@
     <t>資格證書的編碼表示法</t>
   </si>
   <si>
-    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
-  </si>
-  <si>
     <t>照護服務提供人員提供服務所具有的具體資格證書；應填入所綁定值集中適合的代碼，確定無適合的代碼才可以使用其他值集的代碼來表示。</t>
   </si>
   <si>
     <t>https://twcore.mohw.gov.tw/ig/twcore/ValueSet/health-professional-sct-tw</t>
   </si>
   <si>
+    <t>./Qualifications.Value</t>
+  </si>
+  <si>
     <t>Practitioner.qualification.period</t>
   </si>
   <si>
@@ -1901,6 +1898,15 @@
   </si>
   <si>
     <t>人類語言；鼓勵使用所綁定值集中的代碼，但不強制一定要使用此值集，你也可使用其他值集的代碼或單純以文字表示。</t>
+  </si>
+  <si>
+    <t>PID-15, NK1-20, LAN-2</t>
+  </si>
+  <si>
+    <t>./languageCommunication</t>
+  </si>
+  <si>
+    <t>./Languages.LanguageSpokenCode</t>
   </si>
 </sst>
 </file>
@@ -2255,7 +2261,7 @@
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="48.5546875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="48.16015625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="87.9765625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="44.90625" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
@@ -4002,7 +4008,7 @@
         <v>20</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K16" t="s" s="2">
         <v>189</v>
@@ -4075,16 +4081,16 @@
         <v>87</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>198</v>
+        <v>20</v>
       </c>
       <c r="AJ16" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>20</v>
@@ -4095,10 +4101,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4124,10 +4130,10 @@
         <v>164</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4207,10 +4213,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4236,10 +4242,10 @@
         <v>134</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4319,10 +4325,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4342,22 +4348,22 @@
         <v>20</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="O19" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>214</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>20</v>
@@ -4406,7 +4412,7 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
@@ -4415,16 +4421,16 @@
         <v>78</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>198</v>
+        <v>20</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>20</v>
@@ -4435,10 +4441,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4464,10 +4470,10 @@
         <v>164</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4547,10 +4553,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4576,13 +4582,13 @@
         <v>134</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4661,10 +4667,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4690,16 +4696,16 @@
         <v>101</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="M22" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="N22" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="O22" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>20</v>
@@ -4709,7 +4715,7 @@
         <v>20</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="T22" t="s" s="2">
         <v>20</v>
@@ -4748,7 +4754,7 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
@@ -4763,10 +4769,10 @@
         <v>99</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>20</v>
@@ -4777,10 +4783,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4806,13 +4812,13 @@
         <v>164</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="M23" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="N23" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4862,7 +4868,7 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
@@ -4877,10 +4883,10 @@
         <v>99</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>20</v>
@@ -4891,10 +4897,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4920,14 +4926,14 @@
         <v>107</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>20</v>
@@ -4937,7 +4943,7 @@
         <v>20</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>20</v>
@@ -4976,7 +4982,7 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -4991,10 +4997,10 @@
         <v>99</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>20</v>
@@ -5005,10 +5011,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5034,10 +5040,10 @@
         <v>164</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -5117,10 +5123,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5146,10 +5152,10 @@
         <v>134</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5227,13 +5233,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>20</v>
@@ -5255,13 +5261,13 @@
         <v>20</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="L27" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>264</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5321,7 +5327,7 @@
         <v>78</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>198</v>
+        <v>263</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>139</v>
@@ -5341,10 +5347,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="B28" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="B28" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5370,10 +5376,10 @@
         <v>164</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5424,7 +5430,7 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
@@ -5453,10 +5459,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="B29" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5482,14 +5488,14 @@
         <v>164</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>272</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>20</v>
@@ -5538,7 +5544,7 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
@@ -5553,10 +5559,10 @@
         <v>99</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AL29" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="AL29" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>20</v>
@@ -5567,10 +5573,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="B30" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="B30" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5593,19 +5599,19 @@
         <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="N30" t="s" s="2">
+      <c r="O30" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>20</v>
@@ -5654,7 +5660,7 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -5669,10 +5675,10 @@
         <v>99</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AL30" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="AL30" t="s" s="2">
-        <v>286</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>20</v>
@@ -5683,10 +5689,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="B31" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5712,16 +5718,16 @@
         <v>164</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="N31" t="s" s="2">
+      <c r="O31" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>20</v>
@@ -5770,7 +5776,7 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -5785,10 +5791,10 @@
         <v>99</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AL31" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="AL31" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>20</v>
@@ -5799,10 +5805,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="B32" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="B32" t="s" s="2">
-        <v>297</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5828,16 +5834,16 @@
         <v>101</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="N32" t="s" s="2">
+      <c r="O32" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>20</v>
@@ -5847,46 +5853,46 @@
         <v>20</v>
       </c>
       <c r="S32" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="T32" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="T32" t="s" s="2">
+      <c r="U32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF32" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="U32" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V32" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W32" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X32" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y32" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z32" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA32" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB32" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC32" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD32" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE32" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF32" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
@@ -5901,13 +5907,13 @@
         <v>99</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AL32" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="AL32" t="s" s="2">
+      <c r="AM32" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>20</v>
@@ -5915,10 +5921,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="B33" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="B33" t="s" s="2">
-        <v>309</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5944,13 +5950,13 @@
         <v>164</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5964,43 +5970,43 @@
         <v>20</v>
       </c>
       <c r="T33" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="U33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF33" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="U33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF33" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -6015,13 +6021,13 @@
         <v>99</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AL33" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="AL33" t="s" s="2">
+      <c r="AM33" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>317</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>20</v>
@@ -6029,10 +6035,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="B34" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="B34" t="s" s="2">
-        <v>319</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6055,13 +6061,13 @@
         <v>88</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6112,7 +6118,7 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
@@ -6127,13 +6133,13 @@
         <v>99</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="AL34" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="AL34" t="s" s="2">
+      <c r="AM34" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>20</v>
@@ -6141,10 +6147,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="B35" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="B35" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6167,16 +6173,16 @@
         <v>88</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>332</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6226,7 +6232,7 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
@@ -6241,13 +6247,13 @@
         <v>99</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="AL35" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="AL35" t="s" s="2">
+      <c r="AM35" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>20</v>
@@ -6255,13 +6261,13 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>145</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D36" t="s" s="2">
         <v>20</v>
@@ -6286,10 +6292,10 @@
         <v>146</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
@@ -6371,7 +6377,7 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>163</v>
@@ -6483,7 +6489,7 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>170</v>
@@ -6597,7 +6603,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>176</v>
@@ -6713,7 +6719,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>188</v>
@@ -6736,7 +6742,7 @@
         <v>20</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K40" t="s" s="2">
         <v>189</v>
@@ -6809,16 +6815,16 @@
         <v>87</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>198</v>
+        <v>20</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>20</v>
@@ -6829,10 +6835,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6858,10 +6864,10 @@
         <v>164</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6941,10 +6947,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6970,10 +6976,10 @@
         <v>134</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7053,10 +7059,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7076,22 +7082,22 @@
         <v>20</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="O43" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>214</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>20</v>
@@ -7140,7 +7146,7 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -7149,16 +7155,16 @@
         <v>78</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>198</v>
+        <v>20</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>20</v>
@@ -7169,10 +7175,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7198,10 +7204,10 @@
         <v>164</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7281,10 +7287,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7310,13 +7316,13 @@
         <v>134</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7395,10 +7401,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7424,16 +7430,16 @@
         <v>101</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="N46" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="O46" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>20</v>
@@ -7443,7 +7449,7 @@
         <v>20</v>
       </c>
       <c r="S46" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="T46" t="s" s="2">
         <v>20</v>
@@ -7482,7 +7488,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
@@ -7497,10 +7503,10 @@
         <v>99</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>20</v>
@@ -7511,10 +7517,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7540,13 +7546,13 @@
         <v>164</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="N47" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7596,7 +7602,7 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
@@ -7611,10 +7617,10 @@
         <v>99</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>20</v>
@@ -7625,10 +7631,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7654,14 +7660,14 @@
         <v>107</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>20</v>
@@ -7671,7 +7677,7 @@
         <v>20</v>
       </c>
       <c r="S48" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="T48" t="s" s="2">
         <v>20</v>
@@ -7710,7 +7716,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
@@ -7725,10 +7731,10 @@
         <v>99</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>20</v>
@@ -7739,10 +7745,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7768,14 +7774,14 @@
         <v>164</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>272</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>20</v>
@@ -7824,7 +7830,7 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
@@ -7839,10 +7845,10 @@
         <v>99</v>
       </c>
       <c r="AK49" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AL49" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="AL49" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>20</v>
@@ -7853,10 +7859,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7879,19 +7885,19 @@
         <v>88</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="N50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>20</v>
@@ -7940,7 +7946,7 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
@@ -7955,10 +7961,10 @@
         <v>99</v>
       </c>
       <c r="AK50" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AL50" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="AL50" t="s" s="2">
-        <v>286</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>20</v>
@@ -7969,10 +7975,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7998,16 +8004,16 @@
         <v>164</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="N51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>20</v>
@@ -8056,7 +8062,7 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
@@ -8071,10 +8077,10 @@
         <v>99</v>
       </c>
       <c r="AK51" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AL51" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="AL51" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>20</v>
@@ -8085,10 +8091,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8114,16 +8120,16 @@
         <v>101</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="M52" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="N52" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="N52" t="s" s="2">
+      <c r="O52" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>20</v>
@@ -8133,46 +8139,46 @@
         <v>20</v>
       </c>
       <c r="S52" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="T52" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF52" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="U52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
@@ -8187,13 +8193,13 @@
         <v>99</v>
       </c>
       <c r="AK52" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AL52" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="AL52" t="s" s="2">
+      <c r="AM52" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>20</v>
@@ -8201,10 +8207,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8230,13 +8236,13 @@
         <v>164</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="M53" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="N53" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8250,43 +8256,43 @@
         <v>20</v>
       </c>
       <c r="T53" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF53" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="U53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF53" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
@@ -8301,13 +8307,13 @@
         <v>99</v>
       </c>
       <c r="AK53" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AL53" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="AL53" t="s" s="2">
+      <c r="AM53" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>317</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>20</v>
@@ -8315,10 +8321,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8341,13 +8347,13 @@
         <v>88</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8398,7 +8404,7 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
@@ -8413,13 +8419,13 @@
         <v>99</v>
       </c>
       <c r="AK54" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="AL54" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="AL54" t="s" s="2">
+      <c r="AM54" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>20</v>
@@ -8427,10 +8433,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8453,16 +8459,16 @@
         <v>88</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="M55" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>332</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8512,7 +8518,7 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
@@ -8527,13 +8533,13 @@
         <v>99</v>
       </c>
       <c r="AK55" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="AL55" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="AL55" t="s" s="2">
+      <c r="AM55" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>20</v>
@@ -8541,13 +8547,13 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B56" t="s" s="2">
         <v>145</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>20</v>
@@ -8572,10 +8578,10 @@
         <v>146</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>367</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
@@ -8657,7 +8663,7 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B57" t="s" s="2">
         <v>163</v>
@@ -8769,7 +8775,7 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B58" t="s" s="2">
         <v>170</v>
@@ -8883,7 +8889,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B59" t="s" s="2">
         <v>176</v>
@@ -8999,7 +9005,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B60" t="s" s="2">
         <v>188</v>
@@ -9022,7 +9028,7 @@
         <v>20</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K60" t="s" s="2">
         <v>189</v>
@@ -9095,16 +9101,16 @@
         <v>87</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>198</v>
+        <v>20</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>20</v>
@@ -9115,10 +9121,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9144,10 +9150,10 @@
         <v>164</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9227,10 +9233,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9256,10 +9262,10 @@
         <v>134</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9339,10 +9345,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9362,22 +9368,22 @@
         <v>20</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="O63" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>214</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>20</v>
@@ -9426,7 +9432,7 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>77</v>
@@ -9435,16 +9441,16 @@
         <v>78</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>198</v>
+        <v>20</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>20</v>
@@ -9455,10 +9461,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9484,10 +9490,10 @@
         <v>164</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9567,10 +9573,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9596,13 +9602,13 @@
         <v>134</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9681,10 +9687,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9710,16 +9716,16 @@
         <v>101</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="N66" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="O66" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>20</v>
@@ -9729,7 +9735,7 @@
         <v>20</v>
       </c>
       <c r="S66" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="T66" t="s" s="2">
         <v>20</v>
@@ -9768,7 +9774,7 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>77</v>
@@ -9783,10 +9789,10 @@
         <v>99</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>20</v>
@@ -9797,10 +9803,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9826,13 +9832,13 @@
         <v>164</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="N67" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9882,7 +9888,7 @@
         <v>20</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>77</v>
@@ -9897,10 +9903,10 @@
         <v>99</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>20</v>
@@ -9911,10 +9917,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9940,14 +9946,14 @@
         <v>107</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>20</v>
@@ -9957,7 +9963,7 @@
         <v>20</v>
       </c>
       <c r="S68" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="T68" t="s" s="2">
         <v>20</v>
@@ -9996,7 +10002,7 @@
         <v>20</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>77</v>
@@ -10011,10 +10017,10 @@
         <v>99</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>20</v>
@@ -10025,10 +10031,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10054,14 +10060,14 @@
         <v>164</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>272</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>20</v>
@@ -10110,7 +10116,7 @@
         <v>20</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>77</v>
@@ -10125,10 +10131,10 @@
         <v>99</v>
       </c>
       <c r="AK69" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AL69" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="AL69" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>20</v>
@@ -10139,10 +10145,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10165,19 +10171,19 @@
         <v>88</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="L70" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="L70" t="s" s="2">
+      <c r="M70" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="N70" t="s" s="2">
+      <c r="O70" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>20</v>
@@ -10226,7 +10232,7 @@
         <v>20</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>77</v>
@@ -10241,10 +10247,10 @@
         <v>99</v>
       </c>
       <c r="AK70" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AL70" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="AL70" t="s" s="2">
-        <v>286</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>20</v>
@@ -10255,10 +10261,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10284,16 +10290,16 @@
         <v>164</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="N71" t="s" s="2">
+      <c r="O71" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>20</v>
@@ -10342,7 +10348,7 @@
         <v>20</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>77</v>
@@ -10357,10 +10363,10 @@
         <v>99</v>
       </c>
       <c r="AK71" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AL71" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="AL71" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>20</v>
@@ -10371,10 +10377,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10400,16 +10406,16 @@
         <v>101</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="M72" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="N72" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="N72" t="s" s="2">
+      <c r="O72" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>20</v>
@@ -10419,46 +10425,46 @@
         <v>20</v>
       </c>
       <c r="S72" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="T72" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF72" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="U72" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V72" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W72" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X72" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y72" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z72" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF72" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>77</v>
@@ -10473,13 +10479,13 @@
         <v>99</v>
       </c>
       <c r="AK72" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AL72" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="AL72" t="s" s="2">
+      <c r="AM72" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="AM72" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>20</v>
@@ -10487,10 +10493,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10516,13 +10522,13 @@
         <v>164</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="M73" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="N73" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10536,43 +10542,43 @@
         <v>20</v>
       </c>
       <c r="T73" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF73" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="U73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF73" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>77</v>
@@ -10587,13 +10593,13 @@
         <v>99</v>
       </c>
       <c r="AK73" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AL73" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="AL73" t="s" s="2">
+      <c r="AM73" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="AM73" t="s" s="2">
-        <v>317</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>20</v>
@@ -10601,10 +10607,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10627,13 +10633,13 @@
         <v>88</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="L74" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="L74" t="s" s="2">
+      <c r="M74" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10684,7 +10690,7 @@
         <v>20</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>77</v>
@@ -10699,13 +10705,13 @@
         <v>99</v>
       </c>
       <c r="AK74" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="AL74" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="AL74" t="s" s="2">
+      <c r="AM74" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>20</v>
@@ -10713,10 +10719,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10739,16 +10745,16 @@
         <v>88</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="L75" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="L75" t="s" s="2">
+      <c r="M75" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>332</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10798,7 +10804,7 @@
         <v>20</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>77</v>
@@ -10813,13 +10819,13 @@
         <v>99</v>
       </c>
       <c r="AK75" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="AL75" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="AL75" t="s" s="2">
+      <c r="AM75" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="AM75" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>20</v>
@@ -10827,13 +10833,13 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B76" t="s" s="2">
         <v>145</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D76" t="s" s="2">
         <v>20</v>
@@ -10858,10 +10864,10 @@
         <v>146</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" t="s" s="2">
@@ -10943,7 +10949,7 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B77" t="s" s="2">
         <v>163</v>
@@ -11055,7 +11061,7 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B78" t="s" s="2">
         <v>170</v>
@@ -11169,7 +11175,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B79" t="s" s="2">
         <v>176</v>
@@ -11285,7 +11291,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B80" t="s" s="2">
         <v>188</v>
@@ -11308,7 +11314,7 @@
         <v>20</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K80" t="s" s="2">
         <v>189</v>
@@ -11381,16 +11387,16 @@
         <v>87</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>198</v>
+        <v>20</v>
       </c>
       <c r="AJ80" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>20</v>
@@ -11401,10 +11407,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11430,10 +11436,10 @@
         <v>164</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -11513,10 +11519,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11542,10 +11548,10 @@
         <v>134</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -11625,10 +11631,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11648,22 +11654,22 @@
         <v>20</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K83" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="L83" t="s" s="2">
+      <c r="N83" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="M83" t="s" s="2">
+      <c r="O83" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>214</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>20</v>
@@ -11712,7 +11718,7 @@
         <v>20</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>77</v>
@@ -11721,16 +11727,16 @@
         <v>78</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>198</v>
+        <v>20</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>20</v>
@@ -11741,10 +11747,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11770,10 +11776,10 @@
         <v>164</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -11853,10 +11859,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11882,13 +11888,13 @@
         <v>134</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -11967,10 +11973,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11996,16 +12002,16 @@
         <v>101</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="N86" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="M86" t="s" s="2">
+      <c r="O86" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>20</v>
@@ -12015,7 +12021,7 @@
         <v>20</v>
       </c>
       <c r="S86" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="T86" t="s" s="2">
         <v>20</v>
@@ -12054,7 +12060,7 @@
         <v>20</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>77</v>
@@ -12069,10 +12075,10 @@
         <v>99</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>20</v>
@@ -12083,10 +12089,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12112,13 +12118,13 @@
         <v>164</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="M87" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="N87" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -12168,7 +12174,7 @@
         <v>20</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>77</v>
@@ -12183,10 +12189,10 @@
         <v>99</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>20</v>
@@ -12197,10 +12203,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12226,14 +12232,14 @@
         <v>107</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>20</v>
@@ -12243,7 +12249,7 @@
         <v>20</v>
       </c>
       <c r="S88" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="T88" t="s" s="2">
         <v>20</v>
@@ -12282,7 +12288,7 @@
         <v>20</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>77</v>
@@ -12297,10 +12303,10 @@
         <v>99</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>20</v>
@@ -12311,10 +12317,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12340,14 +12346,14 @@
         <v>164</v>
       </c>
       <c r="L89" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="M89" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>272</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>20</v>
@@ -12396,7 +12402,7 @@
         <v>20</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>77</v>
@@ -12411,10 +12417,10 @@
         <v>99</v>
       </c>
       <c r="AK89" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AL89" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="AL89" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>20</v>
@@ -12425,10 +12431,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12451,19 +12457,19 @@
         <v>88</v>
       </c>
       <c r="K90" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="L90" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="L90" t="s" s="2">
+      <c r="M90" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="M90" t="s" s="2">
+      <c r="N90" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="N90" t="s" s="2">
+      <c r="O90" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>20</v>
@@ -12512,7 +12518,7 @@
         <v>20</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>77</v>
@@ -12527,10 +12533,10 @@
         <v>99</v>
       </c>
       <c r="AK90" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AL90" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="AL90" t="s" s="2">
-        <v>286</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>20</v>
@@ -12541,10 +12547,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12570,16 +12576,16 @@
         <v>164</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="N91" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="N91" t="s" s="2">
+      <c r="O91" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>20</v>
@@ -12628,7 +12634,7 @@
         <v>20</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>77</v>
@@ -12643,10 +12649,10 @@
         <v>99</v>
       </c>
       <c r="AK91" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AL91" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="AL91" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>20</v>
@@ -12657,10 +12663,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12686,16 +12692,16 @@
         <v>101</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="M92" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="N92" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="N92" t="s" s="2">
+      <c r="O92" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>20</v>
@@ -12708,43 +12714,43 @@
         <v>20</v>
       </c>
       <c r="T92" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="U92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF92" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="U92" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V92" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W92" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X92" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y92" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z92" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA92" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB92" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC92" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD92" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE92" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF92" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>77</v>
@@ -12759,13 +12765,13 @@
         <v>99</v>
       </c>
       <c r="AK92" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AL92" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="AL92" t="s" s="2">
+      <c r="AM92" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="AM92" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>20</v>
@@ -12773,10 +12779,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12802,13 +12808,13 @@
         <v>164</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="M93" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="N93" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -12822,43 +12828,43 @@
         <v>20</v>
       </c>
       <c r="T93" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="U93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF93" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="U93" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V93" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W93" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X93" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y93" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z93" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA93" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB93" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC93" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD93" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE93" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF93" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>77</v>
@@ -12873,13 +12879,13 @@
         <v>99</v>
       </c>
       <c r="AK93" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AL93" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="AL93" t="s" s="2">
+      <c r="AM93" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="AM93" t="s" s="2">
-        <v>317</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>20</v>
@@ -12887,10 +12893,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12913,13 +12919,13 @@
         <v>88</v>
       </c>
       <c r="K94" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="L94" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="L94" t="s" s="2">
+      <c r="M94" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -12970,7 +12976,7 @@
         <v>20</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>77</v>
@@ -12985,13 +12991,13 @@
         <v>99</v>
       </c>
       <c r="AK94" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="AL94" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="AL94" t="s" s="2">
+      <c r="AM94" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="AM94" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>20</v>
@@ -12999,10 +13005,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13025,16 +13031,16 @@
         <v>88</v>
       </c>
       <c r="K95" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="L95" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="L95" t="s" s="2">
+      <c r="M95" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="M95" t="s" s="2">
+      <c r="N95" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>332</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13084,7 +13090,7 @@
         <v>20</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>77</v>
@@ -13099,13 +13105,13 @@
         <v>99</v>
       </c>
       <c r="AK95" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="AL95" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="AL95" t="s" s="2">
+      <c r="AM95" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="AM95" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>20</v>
@@ -13113,10 +13119,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13139,26 +13145,26 @@
         <v>88</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="L96" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="N96" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="M96" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="N96" t="s" s="2">
+      <c r="O96" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="O96" t="s" s="2">
+      <c r="P96" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q96" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="P96" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q96" t="s" s="2">
-        <v>421</v>
-      </c>
       <c r="R96" t="s" s="2">
         <v>20</v>
       </c>
@@ -13202,7 +13208,7 @@
         <v>20</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>77</v>
@@ -13220,21 +13226,21 @@
         <v>20</v>
       </c>
       <c r="AL96" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AM96" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN96" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="AM96" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN96" t="s" s="2">
-        <v>423</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13257,19 +13263,19 @@
         <v>88</v>
       </c>
       <c r="K97" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="L97" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="L97" t="s" s="2">
+      <c r="M97" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="M97" t="s" s="2">
+      <c r="N97" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="N97" t="s" s="2">
+      <c r="O97" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>20</v>
@@ -13318,7 +13324,7 @@
         <v>20</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>77</v>
@@ -13330,16 +13336,16 @@
         <v>20</v>
       </c>
       <c r="AJ97" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AK97" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="AK97" t="s" s="2">
+      <c r="AL97" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="AL97" t="s" s="2">
+      <c r="AM97" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="AM97" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>20</v>
@@ -13347,10 +13353,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13459,10 +13465,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13573,10 +13579,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13602,16 +13608,16 @@
         <v>107</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="M100" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="M100" t="s" s="2">
+      <c r="N100" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="N100" t="s" s="2">
+      <c r="O100" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>440</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>20</v>
@@ -13639,28 +13645,28 @@
         <v>182</v>
       </c>
       <c r="Y100" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="Z100" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="Z100" t="s" s="2">
+      <c r="AA100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF100" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="AA100" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB100" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC100" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD100" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE100" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF100" t="s" s="2">
-        <v>443</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>77</v>
@@ -13675,13 +13681,13 @@
         <v>99</v>
       </c>
       <c r="AK100" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AL100" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="AL100" t="s" s="2">
+      <c r="AM100" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="AM100" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>20</v>
@@ -13689,10 +13695,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13718,16 +13724,16 @@
         <v>164</v>
       </c>
       <c r="L101" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="M101" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="M101" t="s" s="2">
+      <c r="N101" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="N101" t="s" s="2">
+      <c r="O101" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>451</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>20</v>
@@ -13740,61 +13746,61 @@
         <v>20</v>
       </c>
       <c r="T101" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="U101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF101" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="U101" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V101" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W101" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X101" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y101" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z101" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA101" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB101" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC101" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD101" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE101" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF101" t="s" s="2">
+      <c r="AG101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH101" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI101" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="AG101" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH101" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI101" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="AJ101" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK101" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="AL101" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="AL101" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>20</v>
@@ -13805,14 +13811,14 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
@@ -13834,13 +13840,13 @@
         <v>164</v>
       </c>
       <c r="L102" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="M102" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="M102" t="s" s="2">
+      <c r="N102" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -13854,44 +13860,44 @@
         <v>20</v>
       </c>
       <c r="T102" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="U102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF102" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="U102" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V102" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W102" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X102" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y102" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z102" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA102" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB102" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC102" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD102" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE102" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF102" t="s" s="2">
-        <v>463</v>
-      </c>
       <c r="AG102" t="s" s="2">
         <v>77</v>
       </c>
@@ -13899,19 +13905,19 @@
         <v>87</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AJ102" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK102" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AL102" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="AL102" t="s" s="2">
+      <c r="AM102" t="s" s="2">
         <v>465</v>
-      </c>
-      <c r="AM102" t="s" s="2">
-        <v>466</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>20</v>
@@ -13919,14 +13925,14 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
@@ -13948,13 +13954,13 @@
         <v>164</v>
       </c>
       <c r="L103" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="M103" t="s" s="2">
         <v>469</v>
       </c>
-      <c r="M103" t="s" s="2">
+      <c r="N103" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>471</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -13968,43 +13974,43 @@
         <v>20</v>
       </c>
       <c r="T103" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="U103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF103" t="s" s="2">
         <v>472</v>
-      </c>
-      <c r="U103" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V103" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W103" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X103" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y103" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z103" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA103" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB103" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC103" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD103" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE103" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF103" t="s" s="2">
-        <v>473</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>77</v>
@@ -14013,19 +14019,19 @@
         <v>78</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK103" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="AL103" t="s" s="2">
         <v>474</v>
       </c>
-      <c r="AL103" t="s" s="2">
+      <c r="AM103" t="s" s="2">
         <v>475</v>
-      </c>
-      <c r="AM103" t="s" s="2">
-        <v>476</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>20</v>
@@ -14033,10 +14039,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14062,10 +14068,10 @@
         <v>164</v>
       </c>
       <c r="L104" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="M104" t="s" s="2">
         <v>478</v>
-      </c>
-      <c r="M104" t="s" s="2">
-        <v>479</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -14116,7 +14122,7 @@
         <v>20</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>77</v>
@@ -14131,13 +14137,13 @@
         <v>99</v>
       </c>
       <c r="AK104" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="AL104" t="s" s="2">
         <v>481</v>
       </c>
-      <c r="AL104" t="s" s="2">
+      <c r="AM104" t="s" s="2">
         <v>482</v>
-      </c>
-      <c r="AM104" t="s" s="2">
-        <v>483</v>
       </c>
       <c r="AN104" t="s" s="2">
         <v>20</v>
@@ -14145,10 +14151,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14174,10 +14180,10 @@
         <v>164</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -14228,7 +14234,7 @@
         <v>20</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>77</v>
@@ -14243,10 +14249,10 @@
         <v>99</v>
       </c>
       <c r="AK105" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AL105" t="s" s="2">
         <v>487</v>
-      </c>
-      <c r="AL105" t="s" s="2">
-        <v>488</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>20</v>
@@ -14257,10 +14263,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14283,17 +14289,17 @@
         <v>88</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="L106" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="M106" t="s" s="2">
         <v>490</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>491</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>20</v>
@@ -14342,7 +14348,7 @@
         <v>20</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>77</v>
@@ -14357,13 +14363,13 @@
         <v>99</v>
       </c>
       <c r="AK106" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="AL106" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="AL106" t="s" s="2">
-        <v>495</v>
-      </c>
       <c r="AM106" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AN106" t="s" s="2">
         <v>20</v>
@@ -14371,10 +14377,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14397,19 +14403,19 @@
         <v>88</v>
       </c>
       <c r="K107" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="L107" t="s" s="2">
         <v>497</v>
       </c>
-      <c r="L107" t="s" s="2">
+      <c r="M107" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="M107" t="s" s="2">
+      <c r="N107" t="s" s="2">
         <v>499</v>
       </c>
-      <c r="N107" t="s" s="2">
+      <c r="O107" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="O107" t="s" s="2">
-        <v>501</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>20</v>
@@ -14458,7 +14464,7 @@
         <v>20</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>77</v>
@@ -14473,13 +14479,13 @@
         <v>99</v>
       </c>
       <c r="AK107" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="AL107" t="s" s="2">
         <v>502</v>
       </c>
-      <c r="AL107" t="s" s="2">
+      <c r="AM107" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="AM107" t="s" s="2">
-        <v>504</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>20</v>
@@ -14487,10 +14493,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14599,10 +14605,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14713,10 +14719,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14742,10 +14748,10 @@
         <v>107</v>
       </c>
       <c r="L110" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="M110" t="s" s="2">
         <v>508</v>
-      </c>
-      <c r="M110" t="s" s="2">
-        <v>509</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -14775,49 +14781,49 @@
         <v>182</v>
       </c>
       <c r="Y110" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="Z110" t="s" s="2">
         <v>510</v>
       </c>
-      <c r="Z110" t="s" s="2">
+      <c r="AA110" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB110" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC110" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD110" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE110" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF110" t="s" s="2">
         <v>511</v>
       </c>
-      <c r="AA110" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB110" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC110" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD110" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE110" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF110" t="s" s="2">
+      <c r="AG110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH110" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI110" t="s" s="2">
         <v>512</v>
-      </c>
-      <c r="AG110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH110" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI110" t="s" s="2">
-        <v>513</v>
       </c>
       <c r="AJ110" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK110" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="AL110" t="s" s="2">
         <v>514</v>
       </c>
-      <c r="AL110" t="s" s="2">
+      <c r="AM110" t="s" s="2">
         <v>515</v>
-      </c>
-      <c r="AM110" t="s" s="2">
-        <v>516</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>20</v>
@@ -14825,10 +14831,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14854,16 +14860,16 @@
         <v>164</v>
       </c>
       <c r="L111" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="M111" t="s" s="2">
         <v>518</v>
       </c>
-      <c r="M111" t="s" s="2">
+      <c r="N111" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="N111" t="s" s="2">
+      <c r="O111" t="s" s="2">
         <v>520</v>
-      </c>
-      <c r="O111" t="s" s="2">
-        <v>521</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>20</v>
@@ -14912,7 +14918,7 @@
         <v>20</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>77</v>
@@ -14927,13 +14933,13 @@
         <v>99</v>
       </c>
       <c r="AK111" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="AL111" t="s" s="2">
         <v>523</v>
       </c>
-      <c r="AL111" t="s" s="2">
-        <v>524</v>
-      </c>
       <c r="AM111" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AN111" t="s" s="2">
         <v>20</v>
@@ -14941,10 +14947,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14970,16 +14976,16 @@
         <v>107</v>
       </c>
       <c r="L112" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="M112" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="M112" t="s" s="2">
+      <c r="N112" t="s" s="2">
         <v>527</v>
       </c>
-      <c r="N112" t="s" s="2">
+      <c r="O112" t="s" s="2">
         <v>528</v>
-      </c>
-      <c r="O112" t="s" s="2">
-        <v>529</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>20</v>
@@ -15007,28 +15013,28 @@
         <v>182</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="Z112" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="AA112" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB112" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC112" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD112" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE112" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF112" t="s" s="2">
         <v>530</v>
-      </c>
-      <c r="AA112" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB112" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC112" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD112" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE112" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF112" t="s" s="2">
-        <v>531</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>77</v>
@@ -15043,13 +15049,13 @@
         <v>99</v>
       </c>
       <c r="AK112" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="AL112" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AM112" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="AL112" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="AM112" t="s" s="2">
-        <v>533</v>
       </c>
       <c r="AN112" t="s" s="2">
         <v>20</v>
@@ -15057,10 +15063,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15083,16 +15089,16 @@
         <v>88</v>
       </c>
       <c r="K113" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="L113" t="s" s="2">
         <v>535</v>
       </c>
-      <c r="L113" t="s" s="2">
+      <c r="M113" t="s" s="2">
         <v>536</v>
       </c>
-      <c r="M113" t="s" s="2">
+      <c r="N113" t="s" s="2">
         <v>537</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>538</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -15142,7 +15148,7 @@
         <v>20</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>77</v>
@@ -15171,10 +15177,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15197,13 +15203,13 @@
         <v>88</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -15254,7 +15260,7 @@
         <v>20</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>77</v>
@@ -15272,10 +15278,10 @@
         <v>131</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>20</v>
@@ -15283,10 +15289,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15306,22 +15312,22 @@
         <v>20</v>
       </c>
       <c r="J115" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K115" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="L115" t="s" s="2">
         <v>544</v>
       </c>
-      <c r="L115" t="s" s="2">
+      <c r="M115" t="s" s="2">
         <v>545</v>
       </c>
-      <c r="M115" t="s" s="2">
+      <c r="N115" t="s" s="2">
         <v>546</v>
       </c>
-      <c r="N115" t="s" s="2">
+      <c r="O115" t="s" s="2">
         <v>547</v>
-      </c>
-      <c r="O115" t="s" s="2">
-        <v>548</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>20</v>
@@ -15370,7 +15376,7 @@
         <v>20</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>77</v>
@@ -15379,19 +15385,19 @@
         <v>78</v>
       </c>
       <c r="AI115" t="s" s="2">
-        <v>198</v>
+        <v>20</v>
       </c>
       <c r="AJ115" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK115" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="AL115" t="s" s="2">
         <v>549</v>
       </c>
-      <c r="AL115" t="s" s="2">
+      <c r="AM115" t="s" s="2">
         <v>550</v>
-      </c>
-      <c r="AM115" t="s" s="2">
-        <v>551</v>
       </c>
       <c r="AN115" t="s" s="2">
         <v>20</v>
@@ -15399,10 +15405,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15428,14 +15434,14 @@
         <v>107</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>20</v>
@@ -15463,11 +15469,11 @@
         <v>182</v>
       </c>
       <c r="Y116" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="Z116" t="s" s="2">
         <v>555</v>
       </c>
-      <c r="Z116" t="s" s="2">
-        <v>556</v>
-      </c>
       <c r="AA116" t="s" s="2">
         <v>20</v>
       </c>
@@ -15484,7 +15490,7 @@
         <v>20</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>77</v>
@@ -15499,13 +15505,13 @@
         <v>99</v>
       </c>
       <c r="AK116" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="AL116" t="s" s="2">
         <v>557</v>
       </c>
-      <c r="AL116" t="s" s="2">
+      <c r="AM116" t="s" s="2">
         <v>558</v>
-      </c>
-      <c r="AM116" t="s" s="2">
-        <v>559</v>
       </c>
       <c r="AN116" t="s" s="2">
         <v>20</v>
@@ -15513,10 +15519,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15539,17 +15545,17 @@
         <v>88</v>
       </c>
       <c r="K117" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="L117" t="s" s="2">
         <v>561</v>
       </c>
-      <c r="L117" t="s" s="2">
-        <v>562</v>
-      </c>
       <c r="M117" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>20</v>
@@ -15598,7 +15604,7 @@
         <v>20</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>77</v>
@@ -15613,13 +15619,13 @@
         <v>99</v>
       </c>
       <c r="AK117" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="AL117" t="s" s="2">
         <v>564</v>
       </c>
-      <c r="AL117" t="s" s="2">
+      <c r="AM117" t="s" s="2">
         <v>565</v>
-      </c>
-      <c r="AM117" t="s" s="2">
-        <v>566</v>
       </c>
       <c r="AN117" t="s" s="2">
         <v>20</v>
@@ -15627,10 +15633,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15653,17 +15659,17 @@
         <v>20</v>
       </c>
       <c r="K118" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="L118" t="s" s="2">
         <v>568</v>
       </c>
-      <c r="L118" t="s" s="2">
-        <v>569</v>
-      </c>
       <c r="M118" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>20</v>
@@ -15712,7 +15718,7 @@
         <v>20</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>77</v>
@@ -15730,10 +15736,10 @@
         <v>20</v>
       </c>
       <c r="AL118" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AM118" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="AM118" t="s" s="2">
-        <v>572</v>
       </c>
       <c r="AN118" t="s" s="2">
         <v>20</v>
@@ -15741,10 +15747,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -15767,13 +15773,13 @@
         <v>20</v>
       </c>
       <c r="K119" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="L119" t="s" s="2">
         <v>574</v>
       </c>
-      <c r="L119" t="s" s="2">
+      <c r="M119" t="s" s="2">
         <v>575</v>
-      </c>
-      <c r="M119" t="s" s="2">
-        <v>576</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -15824,7 +15830,7 @@
         <v>20</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>77</v>
@@ -15839,13 +15845,13 @@
         <v>99</v>
       </c>
       <c r="AK119" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="AL119" t="s" s="2">
         <v>577</v>
       </c>
-      <c r="AL119" t="s" s="2">
+      <c r="AM119" t="s" s="2">
         <v>578</v>
-      </c>
-      <c r="AM119" t="s" s="2">
-        <v>579</v>
       </c>
       <c r="AN119" t="s" s="2">
         <v>20</v>
@@ -15853,10 +15859,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -15965,10 +15971,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16079,14 +16085,14 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
@@ -16108,10 +16114,10 @@
         <v>134</v>
       </c>
       <c r="L122" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="M122" t="s" s="2">
         <v>584</v>
-      </c>
-      <c r="M122" t="s" s="2">
-        <v>585</v>
       </c>
       <c r="N122" t="s" s="2">
         <v>137</v>
@@ -16166,7 +16172,7 @@
         <v>20</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>77</v>
@@ -16195,10 +16201,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16224,14 +16230,14 @@
         <v>146</v>
       </c>
       <c r="L123" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="M123" t="s" s="2">
         <v>588</v>
-      </c>
-      <c r="M123" t="s" s="2">
-        <v>589</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>20</v>
@@ -16280,7 +16286,7 @@
         <v>20</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>77</v>
@@ -16298,7 +16304,7 @@
         <v>20</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="AM123" t="s" s="2">
         <v>20</v>
@@ -16309,10 +16315,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16338,14 +16344,12 @@
         <v>189</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="N124" t="s" s="2">
-        <v>594</v>
-      </c>
+        <v>592</v>
+      </c>
+      <c r="N124" s="2"/>
       <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
         <v>20</v>
@@ -16373,10 +16377,10 @@
         <v>194</v>
       </c>
       <c r="Y124" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="Z124" t="s" s="2">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="AA124" t="s" s="2">
         <v>20</v>
@@ -16394,7 +16398,7 @@
         <v>20</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>87</v>
@@ -16403,19 +16407,19 @@
         <v>87</v>
       </c>
       <c r="AI124" t="s" s="2">
-        <v>198</v>
+        <v>20</v>
       </c>
       <c r="AJ124" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK124" t="s" s="2">
-        <v>199</v>
+        <v>20</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>200</v>
+        <v>577</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>20</v>
+        <v>595</v>
       </c>
       <c r="AN124" t="s" s="2">
         <v>20</v>
@@ -16423,10 +16427,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16449,17 +16453,17 @@
         <v>20</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>20</v>
@@ -16508,7 +16512,7 @@
         <v>20</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>77</v>
@@ -16526,10 +16530,10 @@
         <v>20</v>
       </c>
       <c r="AL125" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="AM125" t="s" s="2">
         <v>600</v>
-      </c>
-      <c r="AM125" t="s" s="2">
-        <v>601</v>
       </c>
       <c r="AN125" t="s" s="2">
         <v>20</v>
@@ -16537,10 +16541,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16563,13 +16567,13 @@
         <v>20</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -16620,7 +16624,7 @@
         <v>20</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>77</v>
@@ -16638,7 +16642,7 @@
         <v>20</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="AM126" t="s" s="2">
         <v>20</v>
@@ -16649,10 +16653,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -16678,16 +16682,16 @@
         <v>189</v>
       </c>
       <c r="L127" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="M127" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="N127" t="s" s="2">
         <v>606</v>
       </c>
-      <c r="M127" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="N127" t="s" s="2">
+      <c r="O127" t="s" s="2">
         <v>607</v>
-      </c>
-      <c r="O127" t="s" s="2">
-        <v>608</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>20</v>
@@ -16715,7 +16719,7 @@
         <v>112</v>
       </c>
       <c r="Y127" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="Z127" t="s" s="2">
         <v>114</v>
@@ -16736,7 +16740,7 @@
         <v>20</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>77</v>
@@ -16745,19 +16749,19 @@
         <v>78</v>
       </c>
       <c r="AI127" t="s" s="2">
-        <v>198</v>
+        <v>20</v>
       </c>
       <c r="AJ127" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>199</v>
+        <v>609</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>200</v>
+        <v>610</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>20</v>
+        <v>611</v>
       </c>
       <c r="AN127" t="s" s="2">
         <v>20</v>

--- a/docs/StructureDefinition-LTCPractitioner.xlsx
+++ b/docs/StructureDefinition-LTCPractitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T13:32:15+08:00</t>
+    <t>2026-04-03T21:17:06+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LTCPractitioner.xlsx
+++ b/docs/StructureDefinition-LTCPractitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-03T21:17:06+08:00</t>
+    <t>2026-06-25T08:48:04+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
